--- a/public/file/template-rebate.xlsx
+++ b/public/file/template-rebate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\X555\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sribu\slicing rebate fx\demo\frontend\fxpayout-demo\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E59C9C0-C042-49C4-8B0B-13B1DFFAFB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C6ADC-A56E-4C46-9D44-CB41AD1DF781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{EFFCF84B-8333-F845-95FF-7FA7252259D5}"/>
+    <workbookView xWindow="2325" yWindow="2685" windowWidth="15375" windowHeight="8325" xr2:uid="{EFFCF84B-8333-F845-95FF-7FA7252259D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -167,6 +167,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +511,7 @@
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="8">
         <v>5455657</v>
       </c>
       <c r="C2" s="4">

--- a/public/file/template-rebate.xlsx
+++ b/public/file/template-rebate.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sribu\slicing rebate fx\demo\frontend\fxpayout-demo\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sribu\slicing rebate fx\live\slicing-fxpayout\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C17C6ADC-A56E-4C46-9D44-CB41AD1DF781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A649FA-63B3-4495-BC05-8AB418333E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="2685" windowWidth="15375" windowHeight="8325" xr2:uid="{EFFCF84B-8333-F845-95FF-7FA7252259D5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{EFFCF84B-8333-F845-95FF-7FA7252259D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
